--- a/CollectionExport_MINISTRY_OF_TRADE_AND_INDUSTRY_ExportedOn_22_10_2026_21.41.32.xlsx
+++ b/CollectionExport_MINISTRY_OF_TRADE_AND_INDUSTRY_ExportedOn_22_10_2026_21.41.32.xlsx
@@ -1,10 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_3E289399CF230695CAE7234423DD0CEAE8947912" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="CollectionExport" state="visible" r:id="rId4"/>
+    <sheet name="CollectionExport" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -280,28 +284,34 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="12"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -333,8 +343,12 @@
     <border>
       <left/>
       <right/>
-      <top style="thin"/>
-      <bottom style="double"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="double">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -343,9 +357,6 @@
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -364,6 +375,9 @@
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -702,9 +716,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V21"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -714,846 +728,846 @@
     <col min="7" max="22" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
-      <c r="V2" s="1"/>
-    </row>
-    <row r="4" ht="20" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+    </row>
+    <row r="4" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K4" s="3" t="s">
+      <c r="J4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="L4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="M4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="N4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="O4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="P4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Q4" s="3" t="s">
+      <c r="Q4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="R4" s="3" t="s">
+      <c r="R4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="S4" s="3" t="s">
+      <c r="S4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="T4" s="3" t="s">
+      <c r="T4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="U4" s="3" t="s">
+      <c r="U4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="V4" s="3" t="s">
+      <c r="V4" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
         <v>1</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="4">
         <v>20</v>
       </c>
-      <c r="H5" s="5">
-        <v>0</v>
-      </c>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="6"/>
-      <c r="S5" s="6"/>
-      <c r="T5" s="6"/>
-      <c r="U5" s="6"/>
-      <c r="V5" s="7">
+      <c r="H5" s="4">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="5"/>
+      <c r="S5" s="5"/>
+      <c r="T5" s="5"/>
+      <c r="U5" s="5"/>
+      <c r="V5" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
         <v>2</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="5">
-        <v>10</v>
-      </c>
-      <c r="H6" s="5">
-        <v>0</v>
-      </c>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="6"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="7">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
+      <c r="G6" s="4">
+        <v>10</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="5"/>
+      <c r="U6" s="5"/>
+      <c r="V6" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
         <v>3</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="5">
-        <v>10</v>
-      </c>
-      <c r="H7" s="5">
-        <v>0</v>
-      </c>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
-      <c r="U7" s="6"/>
-      <c r="V7" s="7">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
+      <c r="G7" s="4">
+        <v>10</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="5"/>
+      <c r="S7" s="5"/>
+      <c r="T7" s="5"/>
+      <c r="U7" s="5"/>
+      <c r="V7" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
         <v>4</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="G8" s="5">
-        <v>10</v>
-      </c>
-      <c r="H8" s="5">
+      <c r="G8" s="4">
+        <v>10</v>
+      </c>
+      <c r="H8" s="4">
         <v>40</v>
       </c>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="6"/>
-      <c r="T8" s="6"/>
-      <c r="U8" s="6"/>
-      <c r="V8" s="7">
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
+      <c r="S8" s="5"/>
+      <c r="T8" s="5"/>
+      <c r="U8" s="5"/>
+      <c r="V8" s="6">
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
         <v>5</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G9" s="5">
-        <v>10</v>
-      </c>
-      <c r="H9" s="5">
-        <v>10</v>
-      </c>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
-      <c r="R9" s="6"/>
-      <c r="S9" s="6"/>
-      <c r="T9" s="6"/>
-      <c r="U9" s="6"/>
-      <c r="V9" s="7">
+      <c r="G9" s="4">
+        <v>10</v>
+      </c>
+      <c r="H9" s="4">
+        <v>10</v>
+      </c>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="5"/>
+      <c r="S9" s="5"/>
+      <c r="T9" s="5"/>
+      <c r="U9" s="5"/>
+      <c r="V9" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
         <v>6</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G10" s="5">
-        <v>10</v>
-      </c>
-      <c r="H10" s="5">
-        <v>0</v>
-      </c>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="6"/>
-      <c r="R10" s="6"/>
-      <c r="S10" s="6"/>
-      <c r="T10" s="6"/>
-      <c r="U10" s="6"/>
-      <c r="V10" s="7">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
+      <c r="G10" s="4">
+        <v>10</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
+      <c r="R10" s="5"/>
+      <c r="S10" s="5"/>
+      <c r="T10" s="5"/>
+      <c r="U10" s="5"/>
+      <c r="V10" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
         <v>7</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G11" s="5">
-        <v>10</v>
-      </c>
-      <c r="H11" s="5">
-        <v>10</v>
-      </c>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="6"/>
-      <c r="R11" s="6"/>
-      <c r="S11" s="6"/>
-      <c r="T11" s="6"/>
-      <c r="U11" s="6"/>
-      <c r="V11" s="7">
+      <c r="G11" s="4">
+        <v>10</v>
+      </c>
+      <c r="H11" s="4">
+        <v>10</v>
+      </c>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5"/>
+      <c r="S11" s="5"/>
+      <c r="T11" s="5"/>
+      <c r="U11" s="5"/>
+      <c r="V11" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
         <v>8</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="G12" s="5">
-        <v>10</v>
-      </c>
-      <c r="H12" s="5">
+      <c r="G12" s="4">
+        <v>10</v>
+      </c>
+      <c r="H12" s="4">
         <v>500</v>
       </c>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="6"/>
-      <c r="R12" s="6"/>
-      <c r="S12" s="6"/>
-      <c r="T12" s="6"/>
-      <c r="U12" s="6"/>
-      <c r="V12" s="7">
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="5"/>
+      <c r="S12" s="5"/>
+      <c r="T12" s="5"/>
+      <c r="U12" s="5"/>
+      <c r="V12" s="6">
         <v>510</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
         <v>9</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="G13" s="5">
-        <v>10</v>
-      </c>
-      <c r="H13" s="5">
+      <c r="G13" s="4">
+        <v>10</v>
+      </c>
+      <c r="H13" s="4">
         <v>40</v>
       </c>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="6"/>
-      <c r="S13" s="6"/>
-      <c r="T13" s="6"/>
-      <c r="U13" s="6"/>
-      <c r="V13" s="7">
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="5"/>
+      <c r="S13" s="5"/>
+      <c r="T13" s="5"/>
+      <c r="U13" s="5"/>
+      <c r="V13" s="6">
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
-        <v>10</v>
-      </c>
-      <c r="B14" s="4" t="s">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <v>10</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="4">
         <v>50</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H14" s="4">
         <v>150</v>
       </c>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
-      <c r="Q14" s="6"/>
-      <c r="R14" s="6"/>
-      <c r="S14" s="6"/>
-      <c r="T14" s="6"/>
-      <c r="U14" s="6"/>
-      <c r="V14" s="7">
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="5"/>
+      <c r="S14" s="5"/>
+      <c r="T14" s="5"/>
+      <c r="U14" s="5"/>
+      <c r="V14" s="6">
         <v>200</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
         <v>11</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="4">
         <v>50</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15" s="4">
         <v>150</v>
       </c>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6"/>
-      <c r="Q15" s="6"/>
-      <c r="R15" s="6"/>
-      <c r="S15" s="6"/>
-      <c r="T15" s="6"/>
-      <c r="U15" s="6"/>
-      <c r="V15" s="7">
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="5"/>
+      <c r="S15" s="5"/>
+      <c r="T15" s="5"/>
+      <c r="U15" s="5"/>
+      <c r="V15" s="6">
         <v>200</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
         <v>12</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G16" s="4">
         <v>50</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H16" s="4">
         <v>750</v>
       </c>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="6"/>
-      <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
-      <c r="Q16" s="6"/>
-      <c r="R16" s="6"/>
-      <c r="S16" s="6"/>
-      <c r="T16" s="6"/>
-      <c r="U16" s="6"/>
-      <c r="V16" s="7">
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="5"/>
+      <c r="S16" s="5"/>
+      <c r="T16" s="5"/>
+      <c r="U16" s="5"/>
+      <c r="V16" s="6">
         <v>800</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
         <v>13</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="G17" s="5">
-        <v>10</v>
-      </c>
-      <c r="H17" s="5">
+      <c r="G17" s="4">
+        <v>10</v>
+      </c>
+      <c r="H17" s="4">
         <v>100</v>
       </c>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="6"/>
-      <c r="O17" s="6"/>
-      <c r="P17" s="6"/>
-      <c r="Q17" s="6"/>
-      <c r="R17" s="6"/>
-      <c r="S17" s="6"/>
-      <c r="T17" s="6"/>
-      <c r="U17" s="6"/>
-      <c r="V17" s="7">
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="5"/>
+      <c r="R17" s="5"/>
+      <c r="S17" s="5"/>
+      <c r="T17" s="5"/>
+      <c r="U17" s="5"/>
+      <c r="V17" s="6">
         <v>110</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
         <v>14</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18" s="4">
         <v>20</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H18" s="4">
         <v>30</v>
       </c>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="6"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6"/>
-      <c r="Q18" s="6"/>
-      <c r="R18" s="6"/>
-      <c r="S18" s="6"/>
-      <c r="T18" s="6"/>
-      <c r="U18" s="6"/>
-      <c r="V18" s="7">
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="5"/>
+      <c r="R18" s="5"/>
+      <c r="S18" s="5"/>
+      <c r="T18" s="5"/>
+      <c r="U18" s="5"/>
+      <c r="V18" s="6">
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A19" s="4">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
         <v>15</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="G19" s="5">
-        <v>10</v>
-      </c>
-      <c r="H19" s="5">
-        <v>10</v>
-      </c>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="6"/>
-      <c r="O19" s="6"/>
-      <c r="P19" s="6"/>
-      <c r="Q19" s="6"/>
-      <c r="R19" s="6"/>
-      <c r="S19" s="6"/>
-      <c r="T19" s="6"/>
-      <c r="U19" s="6"/>
-      <c r="V19" s="7">
+      <c r="G19" s="4">
+        <v>10</v>
+      </c>
+      <c r="H19" s="4">
+        <v>10</v>
+      </c>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5"/>
+      <c r="R19" s="5"/>
+      <c r="S19" s="5"/>
+      <c r="T19" s="5"/>
+      <c r="U19" s="5"/>
+      <c r="V19" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A20" s="4">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
         <v>16</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="G20" s="5">
-        <v>10</v>
-      </c>
-      <c r="H20" s="5">
+      <c r="G20" s="4">
+        <v>10</v>
+      </c>
+      <c r="H20" s="4">
         <v>100</v>
       </c>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="6"/>
-      <c r="O20" s="6"/>
-      <c r="P20" s="6"/>
-      <c r="Q20" s="6"/>
-      <c r="R20" s="6"/>
-      <c r="S20" s="6"/>
-      <c r="T20" s="6"/>
-      <c r="U20" s="6"/>
-      <c r="V20" s="7">
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="5"/>
+      <c r="R20" s="5"/>
+      <c r="S20" s="5"/>
+      <c r="T20" s="5"/>
+      <c r="U20" s="5"/>
+      <c r="V20" s="6">
         <v>110</v>
       </c>
     </row>
-    <row r="21" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B21" s="8" t="s">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B21" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G21" s="8">
         <v>300</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H21" s="8">
         <v>1890</v>
       </c>
-      <c r="I21" s="9">
-        <v>0</v>
-      </c>
-      <c r="J21" s="9">
-        <v>0</v>
-      </c>
-      <c r="K21" s="9">
-        <v>0</v>
-      </c>
-      <c r="L21" s="9">
-        <v>0</v>
-      </c>
-      <c r="M21" s="9">
-        <v>0</v>
-      </c>
-      <c r="N21" s="9">
-        <v>0</v>
-      </c>
-      <c r="O21" s="9">
-        <v>0</v>
-      </c>
-      <c r="P21" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="9">
-        <v>0</v>
-      </c>
-      <c r="R21" s="9">
-        <v>0</v>
-      </c>
-      <c r="S21" s="9">
-        <v>0</v>
-      </c>
-      <c r="T21" s="9">
-        <v>0</v>
-      </c>
-      <c r="U21" s="9">
-        <v>0</v>
-      </c>
-      <c r="V21" s="9">
+      <c r="I21" s="8">
+        <v>0</v>
+      </c>
+      <c r="J21" s="8">
+        <v>0</v>
+      </c>
+      <c r="K21" s="8">
+        <v>0</v>
+      </c>
+      <c r="L21" s="8">
+        <v>0</v>
+      </c>
+      <c r="M21" s="8">
+        <v>0</v>
+      </c>
+      <c r="N21" s="8">
+        <v>0</v>
+      </c>
+      <c r="O21" s="8">
+        <v>0</v>
+      </c>
+      <c r="P21" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="8">
+        <v>0</v>
+      </c>
+      <c r="R21" s="8">
+        <v>0</v>
+      </c>
+      <c r="S21" s="8">
+        <v>0</v>
+      </c>
+      <c r="T21" s="8">
+        <v>0</v>
+      </c>
+      <c r="U21" s="8">
+        <v>0</v>
+      </c>
+      <c r="V21" s="8">
         <v>2190</v>
       </c>
     </row>
@@ -1562,6 +1576,6 @@
     <mergeCell ref="A1:V2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>